--- a/output/topology_excel/6557.xlsx
+++ b/output/topology_excel/6557.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,32 +608,32 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t>Wall</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>301</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
         <v>12</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>300</v>
+        <v>343</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>140</v>
+        <v>229</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>387</v>
+        <v>183</v>
       </c>
       <c r="F14" t="n">
-        <v>239</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>346</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="F19" t="n">
         <v>12</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
         <v>12</v>
@@ -905,7 +905,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
@@ -927,7 +927,7 @@
         <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="F24" t="n">
         <v>18</v>
@@ -968,24 +968,112 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>375</v>
+      </c>
+      <c r="F25" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>10</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>230</v>
-      </c>
-      <c r="F25" t="n">
-        <v>35</v>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>227</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>134</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>562</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>132</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/6557.xlsx
+++ b/output/topology_excel/6557.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
         <v>375</v>
       </c>
       <c r="F25" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
